--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$21</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,63 +253,107 @@
 </t>
   </si>
   <si>
-    <t>Nach dem Alter in Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}moped-inv-Altersgruppe-1:If 'neugeborenes' is true then 'beiZugang' must be age group 0. {$this.extension('neugeborenes') = true implies $this.extension('beiZugang') = '0'}</t>
+  </si>
+  <si>
+    <t>Extension.id</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Extension.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Extension.id</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Extension.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
+    <t>Extension.extension:beiZugang</t>
+  </si>
+  <si>
+    <t>beiZugang</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Altersgruppe bei Zugang</t>
+  </si>
+  <si>
+    <t>Nach dem Alter in Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiZugang.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiZugang.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
+    <t>Extension.extension:beiZugang.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.url</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -322,26 +369,35 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Extension.extension:beiZugang.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://example.org/ValueSet/moped-altersgruppe-valueset</t>
+  </si>
+  <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://example.org/ValueSet/moped-altersgruppe-valueset</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -350,6 +406,56 @@
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
+  </si>
+  <si>
+    <t>Extension.extension:beiEntlassung</t>
+  </si>
+  <si>
+    <t>beiEntlassung</t>
+  </si>
+  <si>
+    <t>Altersgruppe bei Entlassung</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiEntlassung.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiEntlassung.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiEntlassung.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:beiEntlassung.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:neugeborenes</t>
+  </si>
+  <si>
+    <t>neugeborenes</t>
+  </si>
+  <si>
+    <t>Ein Patient wird als Neugeborenes bezeichnet, wenn das Alter zum Zugangszeitpunkt auf die Abteilung &lt;28 Tage ist.</t>
+  </si>
+  <si>
+    <t>Extension.extension:neugeborenes.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:neugeborenes.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:neugeborenes.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:neugeborenes.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
   </si>
 </sst>
 </file>
@@ -478,6 +584,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -659,20 +780,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="42.921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.19921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -813,7 +934,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
@@ -847,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -910,18 +1031,18 @@
         <v>19</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" hidden="true">
+      <c r="A3" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AK2" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,25 +1053,25 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,41 +1122,41 @@
         <v>19</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AG3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI3" t="s" s="2">
+      <c r="AJ3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AJ3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK3" t="s" s="2">
+    </row>
+    <row r="4" hidden="true">
+      <c r="A4" t="s" s="2">
         <v>87</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>19</v>
@@ -1050,12 +1171,14 @@
         <v>89</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>19</v>
@@ -1092,19 +1215,19 @@
         <v>19</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1116,32 +1239,34 @@
         <v>19</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="D5" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>19</v>
@@ -1150,24 +1275,22 @@
         <v>19</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>99</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>19</v>
@@ -1209,30 +1332,30 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1243,25 +1366,25 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="H6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1288,47 +1411,1620 @@
         <v>19</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" t="s" s="2">
+      <c r="B7" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH6" t="s" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" hidden="true">
+      <c r="A9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Y9" s="2"/>
+      <c r="Z9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
+      <c r="A10" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" hidden="true">
+      <c r="A11" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI6" t="s" s="2">
+      <c r="L11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK6" t="s" s="2">
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>100</v>
       </c>
+      <c r="I15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK21">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI20">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T14:30:40+00:00</t>
+    <t>2024-12-13T08:39:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA (https://www.elga.gv.at/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDTransferEncounter#Encounter</t>
+    <t>element:http://example.org/StructureDefinition/MopedTransferEncounter#Encounter</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-altersgruppe</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-altersgruppe</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MopedTransferEncounter#Encounter</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedTransferEncounter#Encounter.admission</t>
   </si>
   <si>
     <t>ID</t>
@@ -394,7 +394,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-altersgruppe-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Altersgruppe</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -808,7 +808,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.84765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-altersgruppe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
